--- a/data/trans_dic/P62A$jubilacion-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P62A$jubilacion-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, recibe una pensión de jubilación</t>
+          <t>Población que, al menos, percibe una pensión de jubilación (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>75,03; 94,35</t>
+          <t>74,19; 94,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>55,82; 79,53</t>
+          <t>56,1; 79,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>68,79; 89,55</t>
+          <t>67,06; 89,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44,54; 77,17</t>
+          <t>42,57; 77,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27,79; 60,52</t>
+          <t>27,59; 59,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,48; 50,46</t>
+          <t>25,9; 50,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,28; 57,88</t>
+          <t>30,01; 57,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,1; 29,0</t>
+          <t>9,36; 29,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>58,59; 77,69</t>
+          <t>58,52; 78,15</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45,64; 63,63</t>
+          <t>45,58; 63,3</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51,98; 71,48</t>
+          <t>52,85; 70,6</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27,78; 48,73</t>
+          <t>27,1; 47,87</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>75,49; 89,91</t>
+          <t>75,2; 89,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>63,56; 79,25</t>
+          <t>62,41; 79,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72,05; 85,67</t>
+          <t>72,38; 85,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56,51; 73,66</t>
+          <t>55,32; 73,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,68; 36,3</t>
+          <t>16,52; 35,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,43; 23,79</t>
+          <t>8,4; 24,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,49; 39,96</t>
+          <t>19,39; 39,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,18; 31,94</t>
+          <t>20,78; 32,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>53,57; 67,51</t>
+          <t>53,3; 67,56</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41,82; 56,63</t>
+          <t>42,5; 56,88</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53,09; 66,36</t>
+          <t>53,46; 66,12</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>40,79; 51,81</t>
+          <t>40,78; 52,01</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>83,43; 97,18</t>
+          <t>82,12; 96,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>64,73; 86,52</t>
+          <t>64,6; 85,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>84,09; 96,12</t>
+          <t>84,26; 96,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51,1; 67,82</t>
+          <t>51,83; 68,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25,87; 49,24</t>
+          <t>26,19; 48,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,92; 48,49</t>
+          <t>25,69; 47,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>49,66; 72,88</t>
+          <t>50,15; 73,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>28,42; 43,48</t>
+          <t>28,66; 43,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>58,0; 74,61</t>
+          <t>58,04; 74,3</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48,9; 65,34</t>
+          <t>48,66; 65,05</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>70,79; 84,56</t>
+          <t>69,7; 83,5</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>43,55; 54,72</t>
+          <t>42,37; 54,56</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>84,19; 97,2</t>
+          <t>83,74; 96,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>67,34; 85,15</t>
+          <t>67,47; 84,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>74,72; 90,24</t>
+          <t>74,44; 90,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>77,23; 93,58</t>
+          <t>77,02; 93,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32,14; 55,63</t>
+          <t>33,34; 56,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,25; 52,67</t>
+          <t>32,47; 52,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,69; 60,61</t>
+          <t>37,64; 60,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>44,9; 59,78</t>
+          <t>45,59; 59,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>59,78; 75,81</t>
+          <t>60,68; 76,11</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>53,26; 67,61</t>
+          <t>52,61; 66,39</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60,23; 74,65</t>
+          <t>60,34; 75,14</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>63,23; 75,1</t>
+          <t>63,88; 75,34</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>76,65; 95,97</t>
+          <t>75,48; 94,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>68,73; 90,72</t>
+          <t>66,62; 90,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72,67; 90,8</t>
+          <t>71,56; 90,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34,12; 58,49</t>
+          <t>34,63; 59,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,1; 57,04</t>
+          <t>21,42; 55,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,77; 54,57</t>
+          <t>25,21; 54,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,8; 39,94</t>
+          <t>16,35; 40,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>24,54; 41,49</t>
+          <t>24,18; 41,58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>55,12; 76,06</t>
+          <t>55,01; 75,77</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50,73; 70,5</t>
+          <t>51,12; 70,26</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>47,47; 64,92</t>
+          <t>48,89; 66,33</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>31,16; 46,85</t>
+          <t>31,32; 45,64</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>88,26; 100,0</t>
+          <t>88,55; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>72,54; 90,6</t>
+          <t>70,79; 90,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>77,3; 93,58</t>
+          <t>76,82; 93,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>50,57; 67,09</t>
+          <t>49,58; 67,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17,81; 47,12</t>
+          <t>19,29; 45,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>20,58; 45,12</t>
+          <t>21,62; 44,12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,25; 50,27</t>
+          <t>18,47; 50,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,75; 28,22</t>
+          <t>14,5; 27,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>59,34; 76,95</t>
+          <t>59,88; 77,62</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>51,74; 69,56</t>
+          <t>51,52; 69,0</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>57,73; 75,41</t>
+          <t>57,33; 74,93</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>37,18; 48,87</t>
+          <t>36,85; 48,43</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>87,81; 96,74</t>
+          <t>87,99; 96,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>69,93; 83,99</t>
+          <t>70,71; 84,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>81,31; 92,56</t>
+          <t>81,08; 92,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>55,83; 69,84</t>
+          <t>56,09; 70,09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>31,51; 49,95</t>
+          <t>32,18; 49,91</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,31; 47,93</t>
+          <t>31,21; 47,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,08; 54,2</t>
+          <t>37,11; 54,15</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>48,38; 94,39</t>
+          <t>47,99; 93,64</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>63,98; 75,36</t>
+          <t>63,66; 75,05</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>53,44; 64,86</t>
+          <t>52,36; 64,7</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>59,68; 72,17</t>
+          <t>59,99; 71,52</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>55,97; 92,06</t>
+          <t>55,36; 90,72</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>78,7; 90,03</t>
+          <t>78,59; 90,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>69,13; 81,97</t>
+          <t>69,92; 83,05</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>73,76; 85,05</t>
+          <t>74,35; 85,57</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11,17; 19,46</t>
+          <t>11,14; 19,38</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>37,41; 55,25</t>
+          <t>37,96; 56,25</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,93; 45,93</t>
+          <t>30,38; 46,38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,93; 54,05</t>
+          <t>37,29; 53,87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,72; 18,7</t>
+          <t>10,62; 17,99</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>62,95; 74,04</t>
+          <t>62,56; 73,99</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54,43; 65,03</t>
+          <t>54,38; 65,22</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>59,33; 69,23</t>
+          <t>58,74; 69,16</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,16; 17,63</t>
+          <t>12,09; 18,06</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>86,54; 91,23</t>
+          <t>86,53; 91,2</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>73,16; 79,17</t>
+          <t>73,13; 79,45</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>80,8; 86,13</t>
+          <t>80,6; 85,89</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>49,18; 55,22</t>
+          <t>49,34; 55,43</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>35,09; 43,06</t>
+          <t>34,92; 42,89</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>31,81; 39,39</t>
+          <t>32,15; 39,58</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>39,38; 47,21</t>
+          <t>39,12; 47,08</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>30,59; 72,56</t>
+          <t>30,52; 71,91</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>64,44; 69,68</t>
+          <t>64,47; 69,62</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>55,07; 60,04</t>
+          <t>54,9; 60,06</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>63,01; 67,74</t>
+          <t>62,79; 67,48</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>41,78; 65,94</t>
+          <t>41,72; 66,3</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, recibe una pensión de jubilación</t>
+          <t>Población que, al menos, percibe una pensión de jubilación (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>39604; 49805</t>
+          <t>39161; 49786</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>42469; 60505</t>
+          <t>42683; 60124</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>40074; 52165</t>
+          <t>39064; 52213</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10800; 18711</t>
+          <t>10321; 18785</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9871; 21497</t>
+          <t>9799; 21239</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18909; 34722</t>
+          <t>17820; 34989</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16647; 31820</t>
+          <t>16496; 31686</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2834; 9029</t>
+          <t>2914; 9197</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>51737; 68604</t>
+          <t>51676; 69007</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>66129; 92203</t>
+          <t>66046; 91724</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58859; 80940</t>
+          <t>59845; 79941</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15388; 26987</t>
+          <t>15007; 26514</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>91291; 108725</t>
+          <t>90938; 107706</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>84118; 104889</t>
+          <t>82595; 105775</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>107047; 127284</t>
+          <t>107535; 126927</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>76189; 99308</t>
+          <t>74587; 98573</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13215; 28749</t>
+          <t>13087; 28450</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7490; 21147</t>
+          <t>7469; 22071</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18773; 36613</t>
+          <t>17768; 36159</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>24628; 38979</t>
+          <t>25358; 39561</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>107201; 135114</t>
+          <t>106662; 135216</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>92520; 125273</t>
+          <t>94024; 125844</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>127520; 159388</t>
+          <t>128412; 158816</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>104780; 133088</t>
+          <t>104741; 133603</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>62345; 72624</t>
+          <t>61365; 71773</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>53234; 71157</t>
+          <t>53128; 70015</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>75629; 86448</t>
+          <t>75787; 86478</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>46903; 62247</t>
+          <t>47568; 62499</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>17191; 32727</t>
+          <t>17406; 32197</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18831; 36640</t>
+          <t>19412; 36225</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>39679; 58226</t>
+          <t>40070; 58546</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23797; 36408</t>
+          <t>23998; 36442</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>81889; 105337</t>
+          <t>81951; 104904</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>77163; 103112</t>
+          <t>76784; 102645</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>120232; 143610</t>
+          <t>118374; 141808</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>76429; 96036</t>
+          <t>74370; 95759</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>58919; 68025</t>
+          <t>58605; 67336</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>68942; 87178</t>
+          <t>69075; 86393</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>72143; 87133</t>
+          <t>71879; 86927</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>61025; 73945</t>
+          <t>60861; 74032</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20843; 36073</t>
+          <t>21621; 36937</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>33484; 53041</t>
+          <t>32698; 53230</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28408; 46926</t>
+          <t>29144; 47042</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>36235; 48239</t>
+          <t>36790; 48310</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>80599; 102212</t>
+          <t>81815; 102623</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>108159; 137299</t>
+          <t>106835; 134838</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>104792; 129884</t>
+          <t>104979; 130732</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>100984; 119951</t>
+          <t>102017; 120322</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>34695; 43439</t>
+          <t>34167; 42815</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>34331; 45320</t>
+          <t>33280; 45265</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>48483; 60582</t>
+          <t>47744; 60582</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10714; 18365</t>
+          <t>10871; 18825</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7373; 19932</t>
+          <t>7487; 19430</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12118; 25660</t>
+          <t>11852; 25572</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9039; 22845</t>
+          <t>9350; 23214</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10224; 17285</t>
+          <t>10074; 17322</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>44210; 61011</t>
+          <t>44123; 60780</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>49190; 68366</t>
+          <t>49573; 68133</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>58827; 80447</t>
+          <t>60581; 82194</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>22761; 34222</t>
+          <t>22880; 33345</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>55792; 63214</t>
+          <t>55974; 63214</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>53915; 67333</t>
+          <t>52615; 67253</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>57153; 69191</t>
+          <t>56796; 68925</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>40423; 53627</t>
+          <t>39633; 53760</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8465; 22396</t>
+          <t>9168; 21704</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12371; 27119</t>
+          <t>12994; 26521</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8528; 22268</t>
+          <t>8180; 22170</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8842; 16916</t>
+          <t>8691; 16715</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>65712; 85211</t>
+          <t>66314; 85961</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>69550; 93514</t>
+          <t>69261; 92761</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>68258; 89155</t>
+          <t>67782; 88593</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>52009; 68349</t>
+          <t>51539; 67742</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>125419; 138172</t>
+          <t>125666; 137951</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>111266; 133639</t>
+          <t>112495; 134021</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>124950; 142249</t>
+          <t>124598; 142299</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>88593; 110822</t>
+          <t>88996; 111212</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>37473; 59406</t>
+          <t>38276; 59354</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>47005; 71957</t>
+          <t>46857; 71121</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>56620; 82763</t>
+          <t>56673; 82689</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>166370; 324622</t>
+          <t>165025; 322049</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>167481; 197265</t>
+          <t>166634; 196451</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>165264; 200587</t>
+          <t>161917; 200075</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>182848; 221098</t>
+          <t>183803; 219130</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>281293; 462687</t>
+          <t>278221; 455940</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>132330; 151382</t>
+          <t>132137; 152213</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>134592; 159590</t>
+          <t>136125; 161676</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>157538; 181642</t>
+          <t>158795; 182762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>22509; 39237</t>
+          <t>22461; 39068</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>48126; 71078</t>
+          <t>48839; 72362</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>46341; 71123</t>
+          <t>47045; 71826</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>66078; 96701</t>
+          <t>66723; 96385</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>18701; 32625</t>
+          <t>18534; 31390</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>186821; 219746</t>
+          <t>185686; 219600</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>190252; 227291</t>
+          <t>190070; 227976</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>232879; 271720</t>
+          <t>230552; 271467</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>45719; 66299</t>
+          <t>45488; 67914</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>638560; 673151</t>
+          <t>638499; 672924</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>637330; 689653</t>
+          <t>637078; 692109</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>728215; 776258</t>
+          <t>726361; 774060</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>394198; 442602</t>
+          <t>395485; 444252</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>202158; 248046</t>
+          <t>201156; 247086</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>237356; 293882</t>
+          <t>239895; 295315</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>290214; 347978</t>
+          <t>288316; 346981</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>286820; 680323</t>
+          <t>286160; 674187</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>846704; 915506</t>
+          <t>847160; 914828</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>890632; 970909</t>
+          <t>887821; 971263</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1032356; 1109783</t>
+          <t>1028731; 1105522</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>726665; 1146732</t>
+          <t>725456; 1152980</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P62A$jubilacion-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P62A$jubilacion-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>34,92%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>74,19; 94,32</t>
+          <t>72,55; 93,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>56,1; 79,02</t>
+          <t>55,36; 77,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>67,06; 89,63</t>
+          <t>66,84; 90,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42,57; 77,48</t>
+          <t>38,58; 71,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>27,59; 59,8</t>
+          <t>27,8; 61,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,9; 50,85</t>
+          <t>26,3; 50,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,01; 57,64</t>
+          <t>29,17; 57,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>9,36; 29,54</t>
+          <t>9,23; 29,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>58,52; 78,15</t>
+          <t>59,06; 78,15</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45,58; 63,3</t>
+          <t>44,87; 62,09</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52,85; 70,6</t>
+          <t>53,52; 71,44</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>27,1; 47,87</t>
+          <t>26,05; 46,12</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>47,11%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>75,2; 89,07</t>
+          <t>74,87; 89,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>62,41; 79,92</t>
+          <t>64,35; 80,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72,38; 85,43</t>
+          <t>71,34; 85,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55,32; 73,11</t>
+          <t>57,73; 73,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,52; 35,92</t>
+          <t>16,26; 36,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,4; 24,83</t>
+          <t>8,63; 24,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,39; 39,46</t>
+          <t>19,95; 40,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,78; 32,42</t>
+          <t>20,47; 32,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>53,3; 67,56</t>
+          <t>53,51; 67,3</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42,5; 56,88</t>
+          <t>41,98; 56,46</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53,46; 66,12</t>
+          <t>53,41; 66,31</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>40,78; 52,01</t>
+          <t>41,97; 52,76</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>60,4%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,38%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>82,12; 96,05</t>
+          <t>82,64; 97,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>64,6; 85,13</t>
+          <t>66,05; 86,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>84,26; 96,15</t>
+          <t>82,86; 96,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51,83; 68,1</t>
+          <t>51,49; 68,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26,19; 48,44</t>
+          <t>26,49; 49,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>25,69; 47,94</t>
+          <t>24,49; 49,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50,15; 73,28</t>
+          <t>50,42; 73,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>28,66; 43,53</t>
+          <t>28,34; 43,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>58,04; 74,3</t>
+          <t>56,72; 73,38</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48,66; 65,05</t>
+          <t>48,5; 65,59</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>69,7; 83,5</t>
+          <t>70,44; 83,84</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>42,37; 54,56</t>
+          <t>42,95; 54,61</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>70,36%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>83,74; 96,21</t>
+          <t>84,53; 97,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>67,47; 84,38</t>
+          <t>66,91; 84,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>74,44; 90,03</t>
+          <t>74,55; 90,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>77,02; 93,69</t>
+          <t>76,63; 93,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>33,34; 56,96</t>
+          <t>32,49; 56,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,47; 52,86</t>
+          <t>33,1; 53,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,64; 60,76</t>
+          <t>35,2; 60,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>45,59; 59,87</t>
+          <t>45,22; 61,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>60,68; 76,11</t>
+          <t>60,99; 76,22</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52,61; 66,39</t>
+          <t>52,96; 67,29</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60,34; 75,14</t>
+          <t>59,58; 75,23</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>63,88; 75,34</t>
+          <t>64,54; 76,08</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>37,68%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>75,48; 94,59</t>
+          <t>76,16; 95,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>66,62; 90,61</t>
+          <t>68,51; 91,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>71,56; 90,8</t>
+          <t>71,53; 90,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34,63; 59,96</t>
+          <t>32,19; 55,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,42; 55,6</t>
+          <t>21,08; 54,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,21; 54,39</t>
+          <t>26,29; 54,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,35; 40,59</t>
+          <t>16,67; 39,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>24,18; 41,58</t>
+          <t>24,64; 41,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>55,01; 75,77</t>
+          <t>55,17; 75,77</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51,12; 70,26</t>
+          <t>50,39; 71,28</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48,89; 66,33</t>
+          <t>48,0; 65,64</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>31,32; 45,64</t>
+          <t>30,13; 45,61</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,8%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>88,55; 100,0</t>
+          <t>88,31; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>70,79; 90,49</t>
+          <t>72,43; 90,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>76,82; 93,22</t>
+          <t>76,15; 93,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>49,58; 67,25</t>
+          <t>51,29; 68,18</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>19,29; 45,67</t>
+          <t>18,25; 45,89</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,62; 44,12</t>
+          <t>20,46; 44,21</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,47; 50,05</t>
+          <t>19,43; 50,55</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14,5; 27,89</t>
+          <t>14,5; 27,98</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>59,88; 77,62</t>
+          <t>58,79; 76,13</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>51,52; 69,0</t>
+          <t>51,91; 68,52</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>57,33; 74,93</t>
+          <t>57,17; 75,02</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>36,85; 48,43</t>
+          <t>37,38; 48,86</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>58,23%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>87,99; 96,59</t>
+          <t>88,6; 96,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>70,71; 84,23</t>
+          <t>70,53; 84,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>81,08; 92,6</t>
+          <t>81,39; 92,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>56,09; 70,09</t>
+          <t>56,42; 70,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>32,18; 49,91</t>
+          <t>32,69; 51,03</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,21; 47,37</t>
+          <t>31,21; 48,27</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,11; 54,15</t>
+          <t>36,73; 53,9</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>47,99; 93,64</t>
+          <t>45,39; 58,21</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>63,66; 75,05</t>
+          <t>63,37; 74,89</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>52,36; 64,7</t>
+          <t>52,18; 64,85</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>59,99; 71,52</t>
+          <t>60,8; 71,93</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>55,36; 90,72</t>
+          <t>53,57; 62,64</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,59%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>78,59; 90,53</t>
+          <t>79,27; 90,76</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>69,92; 83,05</t>
+          <t>69,92; 82,98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>74,35; 85,57</t>
+          <t>73,77; 85,35</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11,14; 19,38</t>
+          <t>11,52; 19,57</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>37,96; 56,25</t>
+          <t>37,26; 55,89</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30,38; 46,38</t>
+          <t>29,9; 46,42</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,29; 53,87</t>
+          <t>38,13; 53,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,62; 17,99</t>
+          <t>10,35; 18,49</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>62,56; 73,99</t>
+          <t>63,02; 74,28</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54,38; 65,22</t>
+          <t>53,54; 64,9</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>58,74; 69,16</t>
+          <t>58,73; 68,82</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,09; 18,06</t>
+          <t>11,93; 17,95</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>42,62%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>86,53; 91,2</t>
+          <t>86,66; 91,18</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>73,13; 79,45</t>
+          <t>73,21; 79,28</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>80,6; 85,89</t>
+          <t>81,03; 86,07</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>49,34; 55,43</t>
+          <t>49,2; 55,51</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>34,92; 42,89</t>
+          <t>35,11; 43,37</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>32,15; 39,58</t>
+          <t>32,34; 39,53</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>39,12; 47,08</t>
+          <t>39,17; 47,07</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>30,52; 71,91</t>
+          <t>29,69; 34,73</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>64,47; 69,62</t>
+          <t>64,7; 69,99</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>54,9; 60,06</t>
+          <t>54,96; 60,06</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>62,79; 67,48</t>
+          <t>63,1; 67,69</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>41,72; 66,3</t>
+          <t>40,72; 44,61</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15162</t>
+          <t>14345</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5533</t>
+          <t>5447</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>20695</t>
+          <t>19792</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>39161; 49786</t>
+          <t>38297; 49587</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>42683; 60124</t>
+          <t>42118; 59132</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39064; 52213</t>
+          <t>38933; 52636</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10321; 18785</t>
+          <t>9765; 18190</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9799; 21239</t>
+          <t>9875; 21702</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17820; 34989</t>
+          <t>18094; 34408</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16496; 31686</t>
+          <t>16037; 31385</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2914; 9197</t>
+          <t>2896; 9127</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>51676; 69007</t>
+          <t>52153; 69007</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>66046; 91724</t>
+          <t>65019; 89959</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>59845; 79941</t>
+          <t>60601; 80894</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15007; 26514</t>
+          <t>14764; 26140</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>87387</t>
+          <t>94210</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>31696</t>
+          <t>33001</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>119083</t>
+          <t>127211</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>90938; 107706</t>
+          <t>90535; 107966</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>82595; 105775</t>
+          <t>85164; 106129</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>107535; 126927</t>
+          <t>105988; 126601</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>74587; 98573</t>
+          <t>82585; 105486</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13087; 28450</t>
+          <t>12882; 28816</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7469; 22071</t>
+          <t>7668; 21626</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17768; 36159</t>
+          <t>18278; 36799</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25358; 39561</t>
+          <t>25993; 40822</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>106662; 135216</t>
+          <t>107089; 134679</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>94024; 125844</t>
+          <t>92867; 124896</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>128412; 158816</t>
+          <t>128297; 159272</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>104741; 133603</t>
+          <t>113336; 142478</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55253</t>
+          <t>54415</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30260</t>
+          <t>30836</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>85513</t>
+          <t>85251</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>61365; 71773</t>
+          <t>61755; 72627</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>53128; 70015</t>
+          <t>54321; 70978</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>75787; 86478</t>
+          <t>74522; 86414</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47568; 62499</t>
+          <t>46389; 61356</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>17406; 32197</t>
+          <t>17606; 32861</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19412; 36225</t>
+          <t>18503; 37095</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>40070; 58546</t>
+          <t>40283; 58409</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23998; 36442</t>
+          <t>24406; 37564</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>81951; 104904</t>
+          <t>80087; 103604</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>76784; 102645</t>
+          <t>76530; 103508</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>118374; 141808</t>
+          <t>119637; 142396</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>74370; 95759</t>
+          <t>75679; 96225</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>68563</t>
+          <t>77217</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>42665</t>
+          <t>45898</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>111227</t>
+          <t>123115</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>58605; 67336</t>
+          <t>59163; 68008</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>69075; 86393</t>
+          <t>68506; 86834</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>71879; 86927</t>
+          <t>71985; 87174</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>60861; 74032</t>
+          <t>68136; 83298</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21621; 36937</t>
+          <t>21065; 36711</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>32698; 53230</t>
+          <t>33331; 53594</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29144; 47042</t>
+          <t>27255; 46777</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>36790; 48310</t>
+          <t>38922; 52636</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>81815; 102623</t>
+          <t>82233; 102774</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>106835; 134838</t>
+          <t>107561; 136651</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>104979; 130732</t>
+          <t>103657; 130882</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>102017; 120322</t>
+          <t>112925; 133127</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14401</t>
+          <t>14783</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13572</t>
+          <t>14126</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>27972</t>
+          <t>28909</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>34167; 42815</t>
+          <t>34475; 43361</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>33280; 45265</t>
+          <t>34225; 45661</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>47744; 60582</t>
+          <t>47723; 60457</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10871; 18825</t>
+          <t>10769; 18692</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>7487; 19430</t>
+          <t>7366; 19117</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11852; 25572</t>
+          <t>12363; 25845</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9350; 23214</t>
+          <t>9534; 22839</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10074; 17322</t>
+          <t>10664; 17808</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>44123; 60780</t>
+          <t>44250; 60777</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>49573; 68133</t>
+          <t>48864; 69118</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>60581; 82194</t>
+          <t>59485; 81344</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>22880; 33345</t>
+          <t>23118; 34994</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>47186</t>
+          <t>47105</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>12453</t>
+          <t>12982</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>59639</t>
+          <t>60087</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>55974; 63214</t>
+          <t>55827; 63214</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>52615; 67253</t>
+          <t>53830; 67441</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>56796; 68925</t>
+          <t>56302; 69028</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>39633; 53760</t>
+          <t>40566; 53923</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9168; 21704</t>
+          <t>8676; 21811</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12994; 26521</t>
+          <t>12298; 26573</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8180; 22170</t>
+          <t>8607; 22392</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8691; 16715</t>
+          <t>8886; 17150</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>66314; 85961</t>
+          <t>65102; 84306</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>69261; 92761</t>
+          <t>69780; 92110</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>67782; 88593</t>
+          <t>67598; 88700</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>51539; 67742</t>
+          <t>52474; 68596</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>100078</t>
+          <t>122009</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>275217</t>
+          <t>87029</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>375295</t>
+          <t>209039</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>125666; 137951</t>
+          <t>126543; 138192</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>112495; 134021</t>
+          <t>112211; 134007</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>124598; 142299</t>
+          <t>125073; 142721</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>88996; 111212</t>
+          <t>107432; 133730</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>38276; 59354</t>
+          <t>38872; 60684</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>46857; 71121</t>
+          <t>46857; 72476</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>56673; 82689</t>
+          <t>56086; 82301</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>165025; 322049</t>
+          <t>76517; 98135</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>166634; 196451</t>
+          <t>165862; 196021</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>161917; 200075</t>
+          <t>161370; 200546</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>183803; 219130</t>
+          <t>186269; 220387</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>278221; 455940</t>
+          <t>192309; 224904</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>30350</t>
+          <t>33614</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>24687</t>
+          <t>28299</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>55038</t>
+          <t>61914</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>132137; 152213</t>
+          <t>133283; 152603</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>136125; 161676</t>
+          <t>136132; 161540</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>158795; 182762</t>
+          <t>157559; 182302</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>22461; 39068</t>
+          <t>25819; 43867</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>48839; 72362</t>
+          <t>47941; 71904</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>47045; 71826</t>
+          <t>46303; 71883</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>66723; 96385</t>
+          <t>68216; 96341</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>18534; 31390</t>
+          <t>20709; 37010</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>185686; 219600</t>
+          <t>187035; 220449</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>190070; 227976</t>
+          <t>187138; 226861</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>230552; 271467</t>
+          <t>230524; 270133</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>45488; 67914</t>
+          <t>50624; 76147</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>418379</t>
+          <t>457699</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>436084</t>
+          <t>257619</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>854463</t>
+          <t>715317</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>638499; 672924</t>
+          <t>639437; 672786</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>637078; 692109</t>
+          <t>637702; 690614</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>726361; 774060</t>
+          <t>730260; 775679</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>395485; 444252</t>
+          <t>430253; 485431</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>201156; 247086</t>
+          <t>202254; 249874</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>239895; 295315</t>
+          <t>241307; 294932</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>288316; 346981</t>
+          <t>288692; 346949</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>286160; 674187</t>
+          <t>238666; 279168</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>847160; 914828</t>
+          <t>850179; 919693</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>887821; 971263</t>
+          <t>888787; 971285</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1028731; 1105522</t>
+          <t>1033720; 1108884</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>725456; 1152980</t>
+          <t>683385; 748748</t>
         </is>
       </c>
     </row>
